--- a/ARM Functions/Shop Custom Relocation Patches.xlsx
+++ b/ARM Functions/Shop Custom Relocation Patches.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281EEE2A-D9B0-4048-85D0-61DC787C4172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18120" activeTab="1" xr2:uid="{37D3F7E3-8C43-42EE-90BC-FE11652EB78D}"/>
+    <workbookView xWindow="-16457" yWindow="0" windowWidth="16457" windowHeight="17914" activeTab="1" xr2:uid="{37D3F7E3-8C43-42EE-90BC-FE11652EB78D}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
